--- a/STANDARD OPEN API UAT TESTS(1).xlsx
+++ b/STANDARD OPEN API UAT TESTS(1).xlsx
@@ -854,7 +854,7 @@
       </c>
       <c r="F7" s="29" t="inlineStr">
         <is>
-          <t>201 Created — API user provisioned (X-Reference-Id used as the API user id).</t>
+          <t>201 Created</t>
         </is>
       </c>
       <c r="G7" s="30" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="F8" s="29" t="inlineStr">
         <is>
-          <t>201 Created — {"apiKey":"…"} returned.</t>
+          <t>201 Created</t>
         </is>
       </c>
       <c r="G8" s="30" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F9" s="29" t="inlineStr">
         <is>
-          <t>200 OK — {"access_token":"…","token_type":"access_token","expires_in":3600}.</t>
+          <t>200 OK</t>
         </is>
       </c>
       <c r="G9" s="30" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="F10" s="29" t="inlineStr">
         <is>
-          <t>202 Accepted — request accepted; X-Reference-Id returned as the transaction reference.</t>
+          <t>202 Accepted</t>
         </is>
       </c>
       <c r="G10" s="30" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="F11" s="29" t="inlineStr">
         <is>
-          <t>200 OK — status SUCCESSFUL with financialTransactionId. Failure paths also verified: APPROVAL_REJECTED, EXPIRED, INTERNAL_PROCESSING_ERROR; plus PENDING.</t>
+          <t>200 OK (SUCCESSFUL)</t>
         </is>
       </c>
       <c r="G11" s="30" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="F12" s="29" t="inlineStr">
         <is>
-          <t>Not used by this integration (collection is via Request-to-Pay). Sandbox returned 500 NOT_ALLOWED_TARGET_ENVIRONMENT when probed — not enabled for this subscription.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G12" s="30" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F13" s="29" t="inlineStr">
         <is>
-          <t>Not used by this integration. Sandbox returned 404 RESOURCE_NOT_FOUND when probed — not available for this subscription.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G13" s="30" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="F14" s="29" t="inlineStr">
         <is>
-          <t>N/A — integration does not use Disbursement; not subscribed to the Disbursement product.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G14" s="30" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="F15" s="29" t="inlineStr">
         <is>
-          <t>N/A — integration does not use Disbursement; not subscribed.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G15" s="30" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F16" s="29" t="inlineStr">
         <is>
-          <t>N/A — integration does not use Disbursement; not subscribed.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G16" s="30" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="F17" s="29" t="inlineStr">
         <is>
-          <t>N/A — integration does not use Disbursement; not subscribed.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G17" s="30" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="F18" s="29" t="inlineStr">
         <is>
-          <t>N/A — integration does not use Disbursement; not subscribed.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G18" s="30" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="F19" s="29" t="inlineStr">
         <is>
-          <t>N/A — integration does not use Disbursement; not subscribed.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G19" s="30" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="F20" s="31" t="inlineStr">
         <is>
-          <t>N/A — integration does not use Remittance; not subscribed.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G20" s="32" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F21" s="31" t="inlineStr">
         <is>
-          <t>N/A — integration does not use Remittance; not subscribed.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G21" s="32" t="inlineStr">
